--- a/协作/13-文件所有权.xlsx
+++ b/协作/13-文件所有权.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -930,15 +930,91 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>协作/24-证据/**</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>未冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>协作/25-账本.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>未冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>协作/模板/18-专项审查报告.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>已冻结</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未冻结,已冻结"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"负责人,产品,需求分析,架构契约,实现工程师,代码评审,专项评审,测试验证,集成发布"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/13-文件所有权.xlsx
+++ b/协作/13-文件所有权.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1003,6 +1003,70 @@
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>协作/模板/**（本地缓存，不入库）</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>已冻结</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md（已移出：TEAMODEL 仓库 tag tm-v3.5.1）</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>已冻结</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
         </is>
       </c>
     </row>
